--- a/tests/dicz/fixtures/bag_groups.xlsx
+++ b/tests/dicz/fixtures/bag_groups.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\dicz\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\MyPy\Packages\fltk\tests\dicz\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBD7925-E3F3-40D7-95DB-7B59DD58B44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C892CB9D-C86C-4324-843B-7183BA630622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="77">
   <si>
     <t>label</t>
   </si>
@@ -244,13 +244,16 @@
     <t>main</t>
   </si>
   <si>
-    <t>core,main</t>
-  </si>
-  <si>
     <t>role1</t>
   </si>
   <si>
     <t>role2</t>
+  </si>
+  <si>
+    <t>main,core</t>
+  </si>
+  <si>
+    <t>rule1</t>
   </si>
 </sst>
 </file>
@@ -627,7 +630,7 @@
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
     <col min="2" max="2" width="45.7109375" customWidth="1"/>
     <col min="3" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
     <col min="6" max="6" width="38.5703125" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" customWidth="1"/>
@@ -681,7 +684,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F2" t="s">
         <v>23</v>
@@ -710,8 +713,11 @@
         <f>FALSE()</f>
         <v>0</v>
       </c>
+      <c r="D3" t="s">
+        <v>76</v>
+      </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
@@ -740,8 +746,11 @@
         <f>FALSE()</f>
         <v>0</v>
       </c>
+      <c r="D4" t="s">
+        <v>76</v>
+      </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4" t="s">
         <v>26</v>
@@ -801,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" t="s">
         <v>40</v>
@@ -831,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" t="s">
         <v>41</v>
@@ -861,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" t="s">
         <v>42</v>
@@ -953,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F11" t="s">
         <v>43</v>
@@ -983,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
         <v>44</v>
@@ -1013,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
         <v>45</v>
